--- a/experiment_results/combined_sweep/rtt_bursts_S2_atk1pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S2_atk1pct_wu500000.xlsx
@@ -481,17 +481,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.0</t>
+          <t>00:020.1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>17.10</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15446</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:029.7</t>
+          <t>00:030.0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25775</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -652,22 +652,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:050.0</t>
+          <t>00:050.1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>15.42</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01:000.2</t>
+          <t>00:059.9</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>398</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:020.0</t>
+          <t>01:019.8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:029.7</t>
+          <t>01:030.3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.2</t>
+          <t>01:040.1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1687</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1051,22 +1051,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24447</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02:000.0</t>
+          <t>02:000.1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39320</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36104</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:019.9</t>
+          <t>02:019.7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>32433</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:029.9</t>
+          <t>02:029.8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20397</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:040.0</t>
+          <t>02:040.1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:050.0</t>
+          <t>02:049.9</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,17 +1418,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:054.9</t>
+          <t>02:055.0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">

--- a/experiment_results/combined_sweep/rtt_bursts_S2_atk1pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S2_atk1pct_wu500000.xlsx
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:009.8</t>
+          <t>00:009.7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>336</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -538,22 +538,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15446</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:030.0</t>
+          <t>00:030.1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25775</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:040.0</t>
+          <t>00:039.7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,22 +677,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:050.1</t>
+          <t>00:050.2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>15.42</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -766,22 +766,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.2</t>
+          <t>01:010.1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:019.8</t>
+          <t>01:020.3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,22 +932,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:030.3</t>
+          <t>01:030.0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.1</t>
+          <t>01:040.0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:050.0</t>
+          <t>01:050.1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>24447</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02:000.1</t>
+          <t>01:059.9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>113.3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>201.1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>39320</t>
+          <t>153154</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1153,34 +1153,34 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.0</t>
+          <t>02:010.2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>111.1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>201.8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>36104</t>
+          <t>296709</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1210,34 +1210,34 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:019.7</t>
+          <t>02:020.0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>32433</t>
+          <t>293527</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:029.8</t>
+          <t>02:030.1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20397</t>
+          <t>311848</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:040.1</t>
+          <t>02:040.0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>320149</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:049.9</t>
+          <t>02:050.0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>299628</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1450,22 +1450,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>289246</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
